--- a/monitoring_forms/016_offshore_wind_turbine_condition_monitoring_log--monitoring_forms.xlsx
+++ b/monitoring_forms/016_offshore_wind_turbine_condition_monitoring_log--monitoring_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -895,8 +895,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -924,12 +924,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'offline'}</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Offline'}</t>
+          <t>Offline</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'in_maintenance'}</t>
+          <t>in_maintenance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'In Maintenance'}</t>
+          <t>In Maintenance</t>
         </is>
       </c>
     </row>
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'in_repair'}</t>
+          <t>in_repair</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'In Repair'}</t>
+          <t>In Repair</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'not_resolved'}</t>
+          <t>not_resolved</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Not Resolved'}</t>
+          <t>Not Resolved</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'resolved'}</t>
+          <t>resolved</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Resolved'}</t>
+          <t>Resolved</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'not_scheduled'}</t>
+          <t>not_scheduled</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Not Scheduled'}</t>
+          <t>Not Scheduled</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'scheduled'}</t>
+          <t>scheduled</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Scheduled'}</t>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'done'}</t>
+          <t>done</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Done'}</t>
+          <t>Done</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1264,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'john_smith'}</t>
+          <t>john_smith</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'John Smith'}</t>
+          <t>John Smith</t>
         </is>
       </c>
     </row>
@@ -1281,12 +1281,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'jane_smith'}</t>
+          <t>jane_smith</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Jane Smith'}</t>
+          <t>Jane Smith</t>
         </is>
       </c>
     </row>
